--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -861,7 +861,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M14" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N14" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -905,10 +905,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -922,8 +922,8 @@
       <c r="L15" s="15">
         <v>200</v>
       </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="M15" s="15">
+        <v>200</v>
       </c>
       <c r="N15" s="15">
         <v>-25</v>
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>11.111111111111</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K16" s="15">
-        <v>25</v>
+        <v>6.25</v>
       </c>
       <c r="L16" s="15">
-        <v>-34.782608695652</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="M16" s="15">
-        <v>15.384615384615</v>
+        <v>13.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.941176470588</v>
+        <v>-78.205128205128</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>250</v>
+        <v>80</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-21.052631578947</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I17" s="14">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J17" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K17" s="15">
-        <v>-24</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="M17" s="15">
-        <v>72.727272727272</v>
+        <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>0</v>
+        <v>27.272727272727</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I18" s="14">
         <v>13</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K18" s="15">
-        <v>-23.529411764705</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L18" s="15">
-        <v>44.444444444444</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M18" s="15">
-        <v>-50</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.6</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-9.090909090909</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
         <v>32</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.513513513513</v>
+        <v>3.225806451612</v>
       </c>
       <c r="I19" s="14">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J19" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K19" s="15">
-        <v>-20.370370370370</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="L19" s="15">
-        <v>-47.560975609756</v>
+        <v>-48.514851485148</v>
       </c>
       <c r="M19" s="15">
-        <v>53.571428571428</v>
+        <v>57.575757575757</v>
       </c>
       <c r="N19" s="15">
-        <v>30.303030303030</v>
+        <v>40.540540540540</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>9</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>6</v>
-      </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>15.789473684210</v>
+        <v>9.523809523809</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K20" s="15">
-        <v>8.333333333333</v>
+        <v>29.629629629629</v>
       </c>
       <c r="L20" s="15">
-        <v>-38.095238095238</v>
+        <v>-32.692307692307</v>
       </c>
       <c r="M20" s="15">
-        <v>160</v>
+        <v>218.181818181818</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.792349726776</v>
+        <v>-83.944954128440</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-4</v>
+        <v>45</v>
       </c>
       <c r="F21" s="17">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>-11.881188118811</v>
+        <v>-3.061224489795</v>
       </c>
       <c r="I21" s="17">
-        <v>121</v>
+        <v>151</v>
       </c>
       <c r="J21" s="17">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.029411764705</v>
+        <v>-3.205128205128</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.638418079096</v>
+        <v>-29.107981220657</v>
       </c>
       <c r="M21" s="18">
-        <v>35.955056179775</v>
+        <v>43.809523809523</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.119815668202</v>
+        <v>-70.039682539682</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,29 +1188,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
+      </c>
+      <c r="I22" s="14">
         <v>2</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I22" s="14">
-        <v>1</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>4</v>
-      </c>
-      <c r="G23" s="14">
-        <v>4</v>
-      </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="I23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="14">
         <v>7</v>
       </c>
       <c r="K23" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L23" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="F24" s="14">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="G24" s="14">
         <v>72</v>
       </c>
       <c r="H24" s="15">
-        <v>5.555555555555</v>
+        <v>-25</v>
       </c>
       <c r="I24" s="14">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="J24" s="14">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="K24" s="15">
-        <v>26.086956521739</v>
+        <v>14.414414414414</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.521008403361</v>
+        <v>-7.299270072992</v>
       </c>
       <c r="M24" s="15">
-        <v>78.461538461538</v>
+        <v>64.935064935064</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-71.428571428571</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
+        <v>18</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-38.888888888888</v>
+      </c>
+      <c r="I25" s="14">
         <v>19</v>
       </c>
-      <c r="H25" s="15">
-        <v>-47.368421052631</v>
-      </c>
-      <c r="I25" s="14">
-        <v>16</v>
-      </c>
       <c r="J25" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K25" s="15">
-        <v>-38.461538461538</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="L25" s="15">
-        <v>-64.444444444444</v>
+        <v>-64.150943396226</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.375</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="J26" s="14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>2.222222222222</v>
       </c>
       <c r="L26" s="15">
-        <v>5.882352941176</v>
+        <v>15</v>
       </c>
       <c r="M26" s="15">
-        <v>-5.263157894736</v>
+        <v>9.523809523809</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,10 +1397,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="I28" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J28" s="14">
         <v>3</v>
       </c>
       <c r="K28" s="15">
-        <v>500</v>
+        <v>633.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>3</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1476,7 +1476,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="13" t="s">
-        <v>21</v>
+      <c r="N29" s="15">
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1517,7 +1517,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="13" t="s">
-        <v>21</v>
+      <c r="N30" s="15">
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -851,18 +851,18 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" s="14">
-        <v>3</v>
-      </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
       </c>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -879,13 +879,13 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M14" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N14" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-36.363636363636</v>
+        <v>-30</v>
       </c>
       <c r="I16" s="14">
+        <v>19</v>
+      </c>
+      <c r="J16" s="14">
         <v>17</v>
       </c>
-      <c r="J16" s="14">
-        <v>16</v>
-      </c>
       <c r="K16" s="15">
-        <v>6.25</v>
+        <v>11.764705882352</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.037037037037</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>13.333333333333</v>
+        <v>18.75</v>
       </c>
       <c r="N16" s="15">
-        <v>-78.205128205128</v>
+        <v>-77.906976744186</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,63 +975,63 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>27.777777777777</v>
+        <v>84.615384615384</v>
       </c>
       <c r="I17" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J17" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.666666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="L17" s="15">
-        <v>40</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M17" s="15">
         <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>27.272727272727</v>
+        <v>7.142857142857</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H18" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>13</v>
@@ -1043,13 +1043,13 @@
         <v>-31.578947368421</v>
       </c>
       <c r="L18" s="15">
-        <v>18.181818181818</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.666666666666</v>
+        <v>-59.375</v>
       </c>
       <c r="N18" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.772151898734</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>10</v>
       </c>
       <c r="F19" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G19" s="14">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H19" s="15">
-        <v>3.225806451612</v>
+        <v>0</v>
       </c>
       <c r="I19" s="14">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="J19" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K19" s="15">
-        <v>-13.333333333333</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>-48.514851485148</v>
+        <v>-44.915254237288</v>
       </c>
       <c r="M19" s="15">
-        <v>57.575757575757</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>40.540540540540</v>
+        <v>47.727272727272</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H20" s="15">
-        <v>9.523809523809</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>29.629629629629</v>
+        <v>19.354838709677</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.692307692307</v>
+        <v>-40.322580645161</v>
       </c>
       <c r="M20" s="15">
-        <v>218.181818181818</v>
+        <v>184.615384615385</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.944954128440</v>
+        <v>-84.836065573770</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>45</v>
+        <v>23.529411764705</v>
       </c>
       <c r="F21" s="17">
         <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="H21" s="18">
-        <v>-3.061224489795</v>
+        <v>2.150537634408</v>
       </c>
       <c r="I21" s="17">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="J21" s="17">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.205128205128</v>
+        <v>-1.156069364161</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.107981220657</v>
+        <v>-31.048387096774</v>
       </c>
       <c r="M21" s="18">
-        <v>43.809523809523</v>
+        <v>46.153846153846</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.039682539682</v>
+        <v>-69.787985865724</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,11 +1191,11 @@
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>2</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
         <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>-28.571428571428</v>
+        <v>-40</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M23" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-42.105263157894</v>
+        <v>41.176470588235</v>
       </c>
       <c r="F24" s="14">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="G24" s="14">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H24" s="15">
-        <v>-25</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="I24" s="14">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="J24" s="14">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15">
-        <v>14.414414414414</v>
+        <v>18.75</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.299270072992</v>
+        <v>0</v>
       </c>
       <c r="M24" s="15">
-        <v>64.935064935064</v>
+        <v>52</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
         <v>18</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.888888888888</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J25" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K25" s="15">
-        <v>-34.482758620689</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="L25" s="15">
-        <v>-64.150943396226</v>
+        <v>-56.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>11.111111111111</v>
+        <v>333.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>16.666666666666</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="J26" s="14">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K26" s="15">
-        <v>2.222222222222</v>
+        <v>10.416666666666</v>
       </c>
       <c r="L26" s="15">
-        <v>15</v>
+        <v>26.190476190476</v>
       </c>
       <c r="M26" s="15">
-        <v>9.523809523809</v>
+        <v>12.765957446808</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I28" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="15">
-        <v>633.333333333333</v>
+        <v>500</v>
       </c>
       <c r="L28" s="15">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,17 +1466,17 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
         <v>3</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
-        <v>7</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1507,17 +1507,17 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="14">
-        <v>3</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1617,7 +1617,7 @@
         <v>21</v>
       </c>
       <c r="F33" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
@@ -1626,7 +1626,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
@@ -882,7 +882,7 @@
         <v>300</v>
       </c>
       <c r="M14" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N14" s="15">
         <v>100</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,72 +902,72 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
         <v>2</v>
       </c>
-      <c r="H15" s="15">
-        <v>-50</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-30</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I16" s="14">
         <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>11.764705882352</v>
+        <v>-5</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.666666666666</v>
+        <v>-45.714285714285</v>
       </c>
       <c r="M16" s="15">
-        <v>18.75</v>
+        <v>5.555555555555</v>
       </c>
       <c r="N16" s="15">
-        <v>-77.906976744186</v>
+        <v>-81.372549019607</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>84.615384615384</v>
+        <v>71.428571428571</v>
       </c>
       <c r="I17" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J17" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="K17" s="15">
-        <v>-6.25</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="L17" s="15">
-        <v>42.857142857142</v>
+        <v>45.833333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>100</v>
+        <v>118.75</v>
       </c>
       <c r="N17" s="15">
-        <v>7.142857142857</v>
+        <v>2.941176470588</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="15">
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K18" s="15">
-        <v>-31.578947368421</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
-        <v>-13.333333333333</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="M18" s="15">
-        <v>-59.375</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.772151898734</v>
+        <v>-91.061452513966</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>10</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>0</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I19" s="14">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="J19" s="14">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.142857142857</v>
+        <v>-8.860759493670</v>
       </c>
       <c r="L19" s="15">
-        <v>-44.915254237288</v>
+        <v>-44.615384615384</v>
       </c>
       <c r="M19" s="15">
-        <v>66.666666666666</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N19" s="15">
-        <v>47.727272727272</v>
+        <v>41.176470588235</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20" s="14">
         <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H20" s="15">
-        <v>10.526315789473</v>
+        <v>17.647058823529</v>
       </c>
       <c r="I20" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J20" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K20" s="15">
-        <v>19.354838709677</v>
+        <v>22.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>-40.322580645161</v>
+        <v>-43.421052631578</v>
       </c>
       <c r="M20" s="15">
-        <v>184.615384615385</v>
+        <v>207.142857142857</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.836065573770</v>
+        <v>-84.191176470588</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>23.529411764705</v>
+        <v>4.545454545454</v>
       </c>
       <c r="F21" s="17">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G21" s="17">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H21" s="18">
-        <v>2.150537634408</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="J21" s="17">
-        <v>173</v>
+        <v>195</v>
       </c>
       <c r="K21" s="18">
-        <v>-1.156069364161</v>
+        <v>-0.512820512820</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.048387096774</v>
+        <v>-32.167832167832</v>
       </c>
       <c r="M21" s="18">
-        <v>46.153846153846</v>
+        <v>52.755905511811</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.787985865724</v>
+        <v>-69.969040247678</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J23" s="14">
         <v>10</v>
       </c>
       <c r="K23" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="15">
-        <v>-45.454545454545</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>41.176470588235</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F24" s="14">
         <v>62</v>
       </c>
       <c r="G24" s="14">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H24" s="15">
-        <v>-8.823529411764</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="I24" s="14">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="J24" s="14">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="K24" s="15">
-        <v>18.75</v>
+        <v>13.986013986014</v>
       </c>
       <c r="L24" s="15">
-        <v>0</v>
+        <v>-8.938547486033</v>
       </c>
       <c r="M24" s="15">
-        <v>52</v>
+        <v>48.181818181818</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H25" s="15">
-        <v>-16.666666666666</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J25" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K25" s="15">
-        <v>-21.212121212121</v>
+        <v>-25</v>
       </c>
       <c r="L25" s="15">
-        <v>-56.666666666666</v>
+        <v>-59.701492537313</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>333.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
         <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>66.666666666666</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J26" s="14">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="K26" s="15">
-        <v>10.416666666666</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L26" s="15">
-        <v>26.190476190476</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M26" s="15">
-        <v>12.765957446808</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="H27" s="15">
-        <v>-50</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="I28" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="L28" s="15">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1607,18 +1607,18 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="D33" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F33" s="14">
-        <v>3</v>
-      </c>
       <c r="G33" s="13" t="s">
         <v>20</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -882,7 +882,7 @@
         <v>300</v>
       </c>
       <c r="M14" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N14" s="15">
         <v>100</v>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -926,48 +926,48 @@
         <v>400</v>
       </c>
       <c r="N15" s="15">
-        <v>-16.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-45.454545454545</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.714285714285</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>5.555555555555</v>
+        <v>10.526315789473</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.372549019607</v>
+        <v>-82.051282051282</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
         <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
         <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>71.428571428571</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I17" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J17" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.405405405405</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="L17" s="15">
-        <v>45.833333333333</v>
+        <v>42.307692307692</v>
       </c>
       <c r="M17" s="15">
-        <v>118.75</v>
+        <v>48</v>
       </c>
       <c r="N17" s="15">
-        <v>2.941176470588</v>
+        <v>-13.953488372093</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
         <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-15.789473684210</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.941176470588</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.061452513966</v>
+        <v>-92.195121951219</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>5.555555555555</v>
+        <v>3.030303030303</v>
       </c>
       <c r="I19" s="14">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="J19" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.860759493670</v>
+        <v>-9.195402298850</v>
       </c>
       <c r="L19" s="15">
-        <v>-44.615384615384</v>
+        <v>-45.517241379310</v>
       </c>
       <c r="M19" s="15">
-        <v>71.428571428571</v>
+        <v>58</v>
       </c>
       <c r="N19" s="15">
-        <v>41.176470588235</v>
+        <v>23.4375</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
+        <v>133.333333333333</v>
+      </c>
+      <c r="F20" s="14">
+        <v>24</v>
+      </c>
+      <c r="G20" s="14">
+        <v>14</v>
+      </c>
+      <c r="H20" s="15">
+        <v>71.428571428571</v>
+      </c>
+      <c r="I20" s="14">
         <v>50</v>
       </c>
-      <c r="F20" s="14">
-        <v>20</v>
-      </c>
-      <c r="G20" s="14">
-        <v>17</v>
-      </c>
-      <c r="H20" s="15">
-        <v>17.647058823529</v>
-      </c>
-      <c r="I20" s="14">
-        <v>43</v>
-      </c>
       <c r="J20" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K20" s="15">
-        <v>22.857142857142</v>
+        <v>31.578947368421</v>
       </c>
       <c r="L20" s="15">
-        <v>-43.421052631578</v>
+        <v>-36.708860759493</v>
       </c>
       <c r="M20" s="15">
-        <v>207.142857142857</v>
+        <v>233.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.191176470588</v>
+        <v>-83.660130718954</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>4.545454545454</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="G21" s="17">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H21" s="18">
-        <v>14.285714285714</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I21" s="17">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="J21" s="17">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.512820512820</v>
+        <v>-0.469483568075</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.167832167832</v>
+        <v>-31.612903225806</v>
       </c>
       <c r="M21" s="18">
-        <v>52.755905511811</v>
+        <v>42.281879194630</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.969040247678</v>
+        <v>-71.505376344086</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1198,19 +1198,19 @@
         <v>21</v>
       </c>
       <c r="I22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
         <v>8</v>
       </c>
       <c r="J23" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-38.461538461538</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>-26.666666666666</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F24" s="14">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.060606060606</v>
+        <v>6.153846153846</v>
       </c>
       <c r="I24" s="14">
-        <v>163</v>
+        <v>185</v>
       </c>
       <c r="J24" s="14">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="K24" s="15">
-        <v>13.986013986014</v>
+        <v>17.834394904458</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.938547486033</v>
+        <v>-3.645833333333</v>
       </c>
       <c r="M24" s="15">
-        <v>48.181818181818</v>
+        <v>44.53125</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
         <v>1</v>
       </c>
-      <c r="D25" s="14">
-        <v>3</v>
-      </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>-23.529411764705</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I25" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J25" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K25" s="15">
-        <v>-25</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="L25" s="15">
-        <v>-59.701492537313</v>
+        <v>-57.534246575342</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>58.333333333333</v>
+        <v>48</v>
       </c>
       <c r="I26" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J26" s="14">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="K26" s="15">
-        <v>9.090909090909</v>
+        <v>14.754098360655</v>
       </c>
       <c r="L26" s="15">
-        <v>33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="M26" s="15">
-        <v>11.111111111111</v>
+        <v>12.903225806451</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>300</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J28" s="14">
         <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="L28" s="15">
-        <v>300</v>
+        <v>285.714285714286</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,8 +1496,8 @@
       <c r="L29" s="15">
         <v>600</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="15">
+        <v>600</v>
       </c>
       <c r="N29" s="15">
         <v>600</v>
@@ -1537,8 +1537,8 @@
       <c r="L30" s="15">
         <v>200</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="15">
+        <v>200</v>
       </c>
       <c r="N30" s="15">
         <v>200</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>20</v>
+      <c r="C33" s="14">
+        <v>1</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>
@@ -1626,7 +1626,7 @@
         <v>21</v>
       </c>
       <c r="I33" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>300</v>
       </c>
       <c r="I15" s="14">
+        <v>7</v>
+      </c>
+      <c r="J15" s="14">
         <v>5</v>
       </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
       <c r="K15" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L15" s="15">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M15" s="15">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N15" s="15">
-        <v>-28.571428571428</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14">
         <v>7</v>
       </c>
-      <c r="G16" s="14">
-        <v>9</v>
-      </c>
       <c r="H16" s="15">
-        <v>-22.222222222222</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
         <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.666666666666</v>
+        <v>-39.473684210526</v>
       </c>
       <c r="M16" s="15">
-        <v>10.526315789473</v>
+        <v>9.523809523809</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.051282051282</v>
+        <v>-82.442748091603</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>35.714285714285</v>
+        <v>41.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J17" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.128205128205</v>
+        <v>2.380952380952</v>
       </c>
       <c r="L17" s="15">
-        <v>42.307692307692</v>
+        <v>38.709677419354</v>
       </c>
       <c r="M17" s="15">
-        <v>48</v>
+        <v>59.259259259259</v>
       </c>
       <c r="N17" s="15">
-        <v>-13.953488372093</v>
+        <v>-8.510638297872</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,7 +1019,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
         <v>-100</v>
@@ -1028,28 +1028,28 @@
         <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H18" s="15">
-        <v>-42.857142857142</v>
+        <v>-60</v>
       </c>
       <c r="I18" s="14">
         <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>-33.333333333333</v>
+        <v>-44.827586206896</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.272727272727</v>
+        <v>-36</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.555555555555</v>
+        <v>-56.756756756756</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.195121951219</v>
+        <v>-92.951541850220</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>12</v>
+      </c>
+      <c r="D19" s="14">
         <v>9</v>
       </c>
-      <c r="D19" s="14">
-        <v>8</v>
-      </c>
       <c r="E19" s="15">
-        <v>12.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>3.030303030303</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.195402298850</v>
+        <v>-3.125</v>
       </c>
       <c r="L19" s="15">
-        <v>-45.517241379310</v>
+        <v>-41.139240506329</v>
       </c>
       <c r="M19" s="15">
-        <v>58</v>
+        <v>63.157894736842</v>
       </c>
       <c r="N19" s="15">
-        <v>23.4375</v>
+        <v>32.857142857142</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>133.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
         <v>24</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H20" s="15">
-        <v>71.428571428571</v>
+        <v>60</v>
       </c>
       <c r="I20" s="14">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="J20" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K20" s="15">
-        <v>31.578947368421</v>
+        <v>38.095238095238</v>
       </c>
       <c r="L20" s="15">
-        <v>-36.708860759493</v>
+        <v>-31.764705882352</v>
       </c>
       <c r="M20" s="15">
-        <v>233.333333333333</v>
+        <v>222.222222222222</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.660130718954</v>
+        <v>-82.262996941896</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,57 +1139,57 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E21" s="18">
-        <v>11.111111111111</v>
+        <v>25</v>
       </c>
       <c r="F21" s="17">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="H21" s="18">
-        <v>18.181818181818</v>
+        <v>17.283950617283</v>
       </c>
       <c r="I21" s="17">
-        <v>212</v>
+        <v>244</v>
       </c>
       <c r="J21" s="17">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="K21" s="18">
-        <v>-0.469483568075</v>
+        <v>2.953586497890</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.612903225806</v>
+        <v>-28.023598820059</v>
       </c>
       <c r="M21" s="18">
-        <v>42.281879194630</v>
+        <v>48.780487804878</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.505376344086</v>
+        <v>-69.913686806411</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
         <v>2</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J23" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.333333333333</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L23" s="15">
-        <v>-46.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="M23" s="15">
         <v>0</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>57.142857142857</v>
+        <v>47.368421052631</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="G24" s="14">
         <v>65</v>
       </c>
       <c r="H24" s="15">
-        <v>6.153846153846</v>
+        <v>30.769230769230</v>
       </c>
       <c r="I24" s="14">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="J24" s="14">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="K24" s="15">
-        <v>17.834394904458</v>
+        <v>21.022727272727</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.645833333333</v>
+        <v>0</v>
       </c>
       <c r="M24" s="15">
-        <v>44.53125</v>
+        <v>42</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
         <v>300</v>
       </c>
       <c r="F25" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>36.363636363636</v>
+        <v>90</v>
       </c>
       <c r="I25" s="14">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="J25" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.216216216216</v>
+        <v>0</v>
       </c>
       <c r="L25" s="15">
-        <v>-57.534246575342</v>
+        <v>-50</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>1100</v>
       </c>
       <c r="F26" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>48</v>
+        <v>141.176470588235</v>
       </c>
       <c r="I26" s="14">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="J26" s="14">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K26" s="15">
-        <v>14.754098360655</v>
+        <v>32.258064516129</v>
       </c>
       <c r="L26" s="15">
-        <v>25</v>
+        <v>41.379310344827</v>
       </c>
       <c r="M26" s="15">
-        <v>12.903225806451</v>
+        <v>20.588235294117</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>300</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>350</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>440</v>
+        <v>300</v>
       </c>
       <c r="L28" s="15">
-        <v>285.714285714286</v>
+        <v>154.545454545455</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>3</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>600</v>
       </c>
       <c r="N29" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,15 +1541,15 @@
         <v>200</v>
       </c>
       <c r="N30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="15">
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1607,8 +1607,8 @@
       <c r="A33" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C33" s="14">
-        <v>1</v>
+      <c r="C33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
         <v>2</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
       <c r="E15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>300</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I15" s="14">
+        <v>8</v>
+      </c>
+      <c r="J15" s="14">
         <v>7</v>
       </c>
-      <c r="J15" s="14">
-        <v>5</v>
-      </c>
       <c r="K15" s="15">
-        <v>40</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M15" s="15">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.285714285714</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I16" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L16" s="15">
-        <v>-39.473684210526</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="M16" s="15">
-        <v>9.523809523809</v>
+        <v>-4</v>
       </c>
       <c r="N16" s="15">
-        <v>-82.442748091603</v>
+        <v>-84.105960264900</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
         <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>41.666666666666</v>
+        <v>6.25</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J17" s="14">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="K17" s="15">
-        <v>2.380952380952</v>
+        <v>-2.083333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>38.709677419354</v>
+        <v>27.027027027027</v>
       </c>
       <c r="M17" s="15">
-        <v>59.259259259259</v>
+        <v>67.857142857142</v>
       </c>
       <c r="N17" s="15">
-        <v>-8.510638297872</v>
+        <v>-4.081632653061</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>100</v>
+      </c>
+      <c r="F18" s="14">
         <v>5</v>
       </c>
-      <c r="E18" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="14">
-        <v>4</v>
-      </c>
       <c r="G18" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-60</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>-44.827586206896</v>
+        <v>-40</v>
       </c>
       <c r="L18" s="15">
-        <v>-36</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M18" s="15">
-        <v>-56.756756756756</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.951541850220</v>
+        <v>-92.712550607287</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>7</v>
+      </c>
+      <c r="D19" s="14">
         <v>12</v>
       </c>
-      <c r="D19" s="14">
-        <v>9</v>
-      </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F19" s="14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>11.111111111111</v>
+        <v>2.631578947368</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J19" s="14">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.125</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.139240506329</v>
+        <v>-40.350877192982</v>
       </c>
       <c r="M19" s="15">
-        <v>63.157894736842</v>
+        <v>59.375</v>
       </c>
       <c r="N19" s="15">
-        <v>32.857142857142</v>
+        <v>37.837837837837</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G20" s="14">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
+        <v>9.523809523809</v>
+      </c>
+      <c r="I20" s="14">
         <v>60</v>
       </c>
-      <c r="I20" s="14">
-        <v>58</v>
-      </c>
       <c r="J20" s="14">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="K20" s="15">
-        <v>38.095238095238</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L20" s="15">
-        <v>-31.764705882352</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="M20" s="15">
-        <v>222.222222222222</v>
+        <v>185.714285714286</v>
       </c>
       <c r="N20" s="15">
-        <v>-82.262996941896</v>
+        <v>-83.002832861189</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E21" s="18">
-        <v>25</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="F21" s="17">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G21" s="17">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="H21" s="18">
-        <v>17.283950617283</v>
+        <v>-4.081632653061</v>
       </c>
       <c r="I21" s="17">
-        <v>244</v>
+        <v>263</v>
       </c>
       <c r="J21" s="17">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="K21" s="18">
-        <v>2.953586497890</v>
+        <v>-2.952029520295</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.023598820059</v>
+        <v>-28.726287262872</v>
       </c>
       <c r="M21" s="18">
-        <v>48.780487804878</v>
+        <v>46.111111111111</v>
       </c>
       <c r="N21" s="18">
-        <v>-69.913686806411</v>
+        <v>-70.215175537938</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M22" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
         <v>10</v>
       </c>
       <c r="J23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-23.076923076923</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L23" s="15">
         <v>-37.5</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>28</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>47.368421052631</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F24" s="14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G24" s="14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H24" s="15">
-        <v>30.769230769230</v>
+        <v>36.363636363636</v>
       </c>
       <c r="I24" s="14">
-        <v>213</v>
+        <v>242</v>
       </c>
       <c r="J24" s="14">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="K24" s="15">
-        <v>21.022727272727</v>
+        <v>24.742268041237</v>
       </c>
       <c r="L24" s="15">
-        <v>0</v>
+        <v>0.414937759336</v>
       </c>
       <c r="M24" s="15">
-        <v>42</v>
+        <v>45.783132530120</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>300</v>
+        <v>233.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>90</v>
+        <v>144.444444444444</v>
       </c>
       <c r="I25" s="14">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L25" s="15">
-        <v>-50</v>
+        <v>-47.252747252747</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>1100</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>141.176470588235</v>
+        <v>50</v>
       </c>
       <c r="I26" s="14">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J26" s="14">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="K26" s="15">
-        <v>32.258064516129</v>
+        <v>24.285714285714</v>
       </c>
       <c r="L26" s="15">
-        <v>41.379310344827</v>
+        <v>24.285714285714</v>
       </c>
       <c r="M26" s="15">
-        <v>20.588235294117</v>
+        <v>14.473684210526</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
       <c r="E27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>5</v>
+      </c>
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="15">
+        <v>66.666666666666</v>
+      </c>
+      <c r="I27" s="14">
+        <v>8</v>
+      </c>
+      <c r="J27" s="14">
+        <v>8</v>
+      </c>
+      <c r="K27" s="15">
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
         <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>4</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>300</v>
-      </c>
-      <c r="I27" s="14">
-        <v>7</v>
-      </c>
-      <c r="J27" s="14">
-        <v>6</v>
-      </c>
-      <c r="K27" s="15">
-        <v>16.666666666666</v>
-      </c>
-      <c r="L27" s="15">
-        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-50</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J28" s="14">
         <v>7</v>
       </c>
       <c r="K28" s="15">
-        <v>300</v>
+        <v>328.571428571429</v>
       </c>
       <c r="L28" s="15">
-        <v>154.545454545455</v>
+        <v>114.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-50</v>
+        <v>3</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>14.285714285714</v>
+        <v>57.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="M15" s="15">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="N15" s="15">
-        <v>14.285714285714</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-44.444444444444</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K16" s="15">
-        <v>-7.692307692307</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.842105263157</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="M16" s="15">
-        <v>-4</v>
+        <v>-29.729729729729</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.105960264900</v>
+        <v>-84.146341463414</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
         <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>6.25</v>
+        <v>-6.25</v>
       </c>
       <c r="I17" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J17" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.083333333333</v>
+        <v>-5.660377358490</v>
       </c>
       <c r="L17" s="15">
-        <v>27.027027027027</v>
+        <v>28.205128205128</v>
       </c>
       <c r="M17" s="15">
-        <v>67.857142857142</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-4.081632653061</v>
+        <v>-10.714285714285</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H18" s="15">
-        <v>-54.545454545454</v>
+        <v>-68.75</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-40</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-35.714285714285</v>
+        <v>-27.586206896551</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.631578947368</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.712550607287</v>
+        <v>-92.193308550185</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-41.666666666666</v>
+        <v>-30</v>
       </c>
       <c r="F19" s="14">
+        <v>37</v>
+      </c>
+      <c r="G19" s="14">
         <v>39</v>
       </c>
-      <c r="G19" s="14">
-        <v>38</v>
-      </c>
       <c r="H19" s="15">
-        <v>2.631578947368</v>
+        <v>-5.128205128205</v>
       </c>
       <c r="I19" s="14">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="J19" s="14">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.555555555555</v>
+        <v>-8.474576271186</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.350877192982</v>
+        <v>-43.157894736842</v>
       </c>
       <c r="M19" s="15">
-        <v>59.375</v>
+        <v>56.521739130434</v>
       </c>
       <c r="N19" s="15">
-        <v>37.837837837837</v>
+        <v>24.137931034482</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="F20" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
         <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>9.523809523809</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I20" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J20" s="14">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="K20" s="15">
-        <v>15.384615384615</v>
+        <v>8.928571428571</v>
       </c>
       <c r="L20" s="15">
-        <v>-35.483870967741</v>
+        <v>-35.789473684210</v>
       </c>
       <c r="M20" s="15">
-        <v>185.714285714286</v>
+        <v>125.925925925926</v>
       </c>
       <c r="N20" s="15">
-        <v>-83.002832861189</v>
+        <v>-84.517766497461</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-52.941176470588</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F21" s="17">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H21" s="18">
-        <v>-4.081632653061</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="I21" s="17">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="J21" s="17">
-        <v>271</v>
+        <v>297</v>
       </c>
       <c r="K21" s="18">
-        <v>-2.952029520295</v>
+        <v>-5.387205387205</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.726287262872</v>
+        <v>-29.040404040404</v>
       </c>
       <c r="M21" s="18">
-        <v>46.111111111111</v>
+        <v>36.407766990291</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.215175537938</v>
+        <v>-71.326530612244</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
         <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
         <v>14</v>
       </c>
       <c r="K23" s="15">
-        <v>-28.571428571428</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L23" s="15">
-        <v>-37.5</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="M23" s="15">
-        <v>-9.090909090909</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>55.555555555555</v>
+        <v>76.923076923076</v>
       </c>
       <c r="F24" s="14">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="G24" s="14">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H24" s="15">
-        <v>36.363636363636</v>
+        <v>56.25</v>
       </c>
       <c r="I24" s="14">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="J24" s="14">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="K24" s="15">
-        <v>24.742268041237</v>
+        <v>27.053140096618</v>
       </c>
       <c r="L24" s="15">
-        <v>0.414937759336</v>
+        <v>1.544401544401</v>
       </c>
       <c r="M24" s="15">
-        <v>45.783132530120</v>
+        <v>37.696335078534</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>233.333333333333</v>
+        <v>80</v>
       </c>
       <c r="F25" s="14">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>144.444444444444</v>
+        <v>172.727272727273</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J25" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K25" s="15">
-        <v>14.285714285714</v>
+        <v>21.276595744680</v>
       </c>
       <c r="L25" s="15">
-        <v>-47.252747252747</v>
+        <v>-43.564356435643</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>14</v>
+      </c>
+      <c r="D26" s="14">
         <v>6</v>
       </c>
-      <c r="D26" s="14">
-        <v>8</v>
-      </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>50</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I26" s="14">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="J26" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="K26" s="15">
-        <v>24.285714285714</v>
+        <v>31.578947368421</v>
       </c>
       <c r="L26" s="15">
-        <v>24.285714285714</v>
+        <v>31.578947368421</v>
       </c>
       <c r="M26" s="15">
-        <v>14.473684210526</v>
+        <v>20.481927710843</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+        <v>4</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="I28" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>328.571428571429</v>
+        <v>255.555555555556</v>
       </c>
       <c r="L28" s="15">
-        <v>114.285714285714</v>
+        <v>113.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,31 +902,31 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>57.142857142857</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L15" s="15">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="M15" s="15">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="N15" s="15">
-        <v>37.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
         <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J16" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K16" s="15">
-        <v>-3.703703703703</v>
+        <v>3.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.585365853658</v>
+        <v>-36.956521739130</v>
       </c>
       <c r="M16" s="15">
-        <v>-29.729729729729</v>
+        <v>-21.621621621621</v>
       </c>
       <c r="N16" s="15">
-        <v>-84.146341463414</v>
+        <v>-83.707865168539</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>9</v>
+      </c>
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
-        <v>5</v>
-      </c>
       <c r="E17" s="15">
-        <v>-40</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>-6.25</v>
+        <v>47.058823529411</v>
       </c>
       <c r="I17" s="14">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.660377358490</v>
+        <v>10.714285714285</v>
       </c>
       <c r="L17" s="15">
-        <v>28.205128205128</v>
+        <v>40.909090909090</v>
       </c>
       <c r="M17" s="15">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>-10.714285714285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H18" s="15">
-        <v>-68.75</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
         <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.666666666666</v>
+        <v>-52.272727272727</v>
       </c>
       <c r="L18" s="15">
-        <v>-27.586206896551</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M18" s="15">
-        <v>-46.153846153846</v>
+        <v>-47.5</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.193308550185</v>
+        <v>-92.808219178082</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
         <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H19" s="15">
-        <v>-5.128205128205</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="I19" s="14">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="J19" s="14">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="K19" s="15">
-        <v>-8.474576271186</v>
+        <v>-9.375</v>
       </c>
       <c r="L19" s="15">
-        <v>-43.157894736842</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M19" s="15">
-        <v>56.521739130434</v>
+        <v>61.111111111111</v>
       </c>
       <c r="N19" s="15">
-        <v>24.137931034482</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-75</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G20" s="14">
         <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>-14.285714285714</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I20" s="14">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J20" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K20" s="15">
-        <v>8.928571428571</v>
+        <v>11.864406779661</v>
       </c>
       <c r="L20" s="15">
-        <v>-35.789473684210</v>
+        <v>-34.653465346534</v>
       </c>
       <c r="M20" s="15">
-        <v>125.925925925926</v>
+        <v>120</v>
       </c>
       <c r="N20" s="15">
-        <v>-84.517766497461</v>
+        <v>-85.034013605442</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-30.769230769230</v>
+        <v>12</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G21" s="17">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.725490196078</v>
+        <v>-12.844036697247</v>
       </c>
       <c r="I21" s="17">
-        <v>281</v>
+        <v>310</v>
       </c>
       <c r="J21" s="17">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.387205387205</v>
+        <v>-3.726708074534</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.040404040404</v>
+        <v>-27.738927738927</v>
       </c>
       <c r="M21" s="18">
-        <v>36.407766990291</v>
+        <v>44.186046511627</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.326530612244</v>
+        <v>-71.375807940904</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,14 +1188,14 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="14">
-        <v>2</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1233,10 +1233,10 @@
         <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
         <v>11</v>
@@ -1248,10 +1248,10 @@
         <v>-21.428571428571</v>
       </c>
       <c r="L23" s="15">
-        <v>-38.888888888888</v>
+        <v>-45</v>
       </c>
       <c r="M23" s="15">
-        <v>-15.384615384615</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="E24" s="15">
-        <v>76.923076923076</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="F24" s="14">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="G24" s="14">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H24" s="15">
-        <v>56.25</v>
+        <v>20.833333333333</v>
       </c>
       <c r="I24" s="14">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="J24" s="14">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="K24" s="15">
-        <v>27.053140096618</v>
+        <v>19.213973799126</v>
       </c>
       <c r="L24" s="15">
-        <v>1.544401544401</v>
+        <v>-5.862068965517</v>
       </c>
       <c r="M24" s="15">
-        <v>37.696335078534</v>
+        <v>32.524271844660</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>80</v>
+        <v>-60</v>
       </c>
       <c r="F25" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H25" s="15">
-        <v>172.727272727273</v>
+        <v>55</v>
       </c>
       <c r="I25" s="14">
+        <v>61</v>
+      </c>
+      <c r="J25" s="14">
         <v>57</v>
       </c>
-      <c r="J25" s="14">
-        <v>47</v>
-      </c>
       <c r="K25" s="15">
-        <v>21.276595744680</v>
+        <v>7.017543859649</v>
       </c>
       <c r="L25" s="15">
-        <v>-43.564356435643</v>
+        <v>-47.863247863247</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>133.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F26" s="14">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>85.714285714285</v>
+        <v>59.090909090909</v>
       </c>
       <c r="I26" s="14">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J26" s="14">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="K26" s="15">
-        <v>31.578947368421</v>
+        <v>26.506024096385</v>
       </c>
       <c r="L26" s="15">
-        <v>31.578947368421</v>
+        <v>25</v>
       </c>
       <c r="M26" s="15">
-        <v>20.481927710843</v>
+        <v>20.689655172413</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J27" s="14">
         <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G28" s="14">
         <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="I28" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J28" s="14">
         <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>255.555555555556</v>
+        <v>277.777777777778</v>
       </c>
       <c r="L28" s="15">
-        <v>113.333333333333</v>
+        <v>112.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>600</v>
       </c>
       <c r="N29" s="15">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>200</v>
       </c>
       <c r="N30" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -893,7 +893,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -905,28 +905,28 @@
         <v>7</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>133.333333333333</v>
+        <v>250</v>
       </c>
       <c r="I15" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>71.428571428571</v>
+        <v>100</v>
       </c>
       <c r="L15" s="15">
-        <v>1100</v>
+        <v>1300</v>
       </c>
       <c r="M15" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="N15" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>14.285714285714</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
+        <v>35</v>
+      </c>
+      <c r="J16" s="14">
         <v>29</v>
       </c>
-      <c r="J16" s="14">
-        <v>28</v>
-      </c>
       <c r="K16" s="15">
-        <v>3.571428571428</v>
+        <v>20.689655172413</v>
       </c>
       <c r="L16" s="15">
-        <v>-36.956521739130</v>
+        <v>-23.913043478260</v>
       </c>
       <c r="M16" s="15">
-        <v>-21.621621621621</v>
+        <v>-10.256410256410</v>
       </c>
       <c r="N16" s="15">
-        <v>-83.707865168539</v>
+        <v>-81.283422459893</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>47.058823529411</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I17" s="14">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="K17" s="15">
-        <v>10.714285714285</v>
+        <v>11.475409836065</v>
       </c>
       <c r="L17" s="15">
-        <v>40.909090909090</v>
+        <v>38.775510204081</v>
       </c>
       <c r="M17" s="15">
-        <v>100</v>
+        <v>112.5</v>
       </c>
       <c r="N17" s="15">
-        <v>0</v>
+        <v>1.492537313432</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.272727272727</v>
+        <v>-51.063829787234</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.363636363636</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="M18" s="15">
-        <v>-47.5</v>
+        <v>-43.902439024390</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.808219178082</v>
+        <v>-92.698412698412</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="F19" s="14">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G19" s="14">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="H19" s="15">
-        <v>-17.073170731707</v>
+        <v>-36.734693877551</v>
       </c>
       <c r="I19" s="14">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="J19" s="14">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="K19" s="15">
-        <v>-9.375</v>
+        <v>-14.482758620689</v>
       </c>
       <c r="L19" s="15">
-        <v>-42.857142857142</v>
+        <v>-42.056074766355</v>
       </c>
       <c r="M19" s="15">
-        <v>61.111111111111</v>
+        <v>53.086419753086</v>
       </c>
       <c r="N19" s="15">
-        <v>16</v>
+        <v>10.714285714285</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>5</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-23.809523809523</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="14">
         <v>66</v>
       </c>
       <c r="J20" s="14">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="K20" s="15">
-        <v>11.864406779661</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-34.653465346534</v>
+        <v>-37.735849056603</v>
       </c>
       <c r="M20" s="15">
-        <v>120</v>
+        <v>112.903225806452</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.034013605442</v>
+        <v>-85.987261146496</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E21" s="18">
-        <v>12</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="F21" s="17">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G21" s="17">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H21" s="18">
-        <v>-12.844036697247</v>
+        <v>-25.423728813559</v>
       </c>
       <c r="I21" s="17">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="J21" s="17">
-        <v>322</v>
+        <v>355</v>
       </c>
       <c r="K21" s="18">
-        <v>-3.726708074534</v>
+        <v>-5.915492957746</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.738927738927</v>
+        <v>-25.942350332594</v>
       </c>
       <c r="M21" s="18">
-        <v>44.186046511627</v>
+        <v>45.851528384279</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.375807940904</v>
+        <v>-71.256454388984</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1223,32 +1223,32 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>2</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
+        <v>1</v>
+      </c>
+      <c r="G23" s="14">
         <v>3</v>
       </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-21.428571428571</v>
+        <v>-31.25</v>
       </c>
       <c r="L23" s="15">
-        <v>-45</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="M23" s="15">
         <v>-26.666666666666</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E24" s="15">
-        <v>-59.090909090909</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H24" s="15">
-        <v>20.833333333333</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I24" s="14">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="J24" s="14">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="K24" s="15">
-        <v>19.213973799126</v>
+        <v>16.734693877551</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.862068965517</v>
+        <v>-8.917197452229</v>
       </c>
       <c r="M24" s="15">
-        <v>32.524271844660</v>
+        <v>30</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H25" s="15">
-        <v>55</v>
+        <v>8.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J25" s="14">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K25" s="15">
-        <v>7.017543859649</v>
+        <v>1.587301587301</v>
       </c>
       <c r="L25" s="15">
-        <v>-47.863247863247</v>
+        <v>-50.387596899224</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
         <v>-28.571428571428</v>
       </c>
       <c r="F26" s="14">
+        <v>34</v>
+      </c>
+      <c r="G26" s="14">
         <v>35</v>
       </c>
-      <c r="G26" s="14">
-        <v>22</v>
-      </c>
       <c r="H26" s="15">
-        <v>59.090909090909</v>
+        <v>-2.857142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J26" s="14">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="K26" s="15">
-        <v>26.506024096385</v>
+        <v>17.525773195876</v>
       </c>
       <c r="L26" s="15">
-        <v>25</v>
+        <v>26.666666666666</v>
       </c>
       <c r="M26" s="15">
-        <v>20.689655172413</v>
+        <v>26.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,13 +1385,13 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
         <v>8</v>
@@ -1403,16 +1403,16 @@
         <v>166.666666666667</v>
       </c>
       <c r="I27" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>62.5</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>75</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I28" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>277.777777777778</v>
+        <v>260</v>
       </c>
       <c r="L28" s="15">
-        <v>112.5</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>7</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>600</v>
       </c>
       <c r="L29" s="15">
         <v>600</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>3</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>200</v>
       </c>
       <c r="L30" s="15">
         <v>200</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
-      <c r="H15" s="15">
-        <v>250</v>
+        <v>6</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>14</v>
@@ -923,7 +923,7 @@
         <v>1300</v>
       </c>
       <c r="M15" s="15">
-        <v>600</v>
+        <v>366.666666666667</v>
       </c>
       <c r="N15" s="15">
         <v>75</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>500</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>20.689655172413</v>
+        <v>12.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-23.913043478260</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-10.256410256410</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.283422459893</v>
+        <v>-81.538461538461</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,60 +978,60 @@
         <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F17" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>21.052631578947</v>
+        <v>30</v>
       </c>
       <c r="I17" s="14">
+        <v>74</v>
+      </c>
+      <c r="J17" s="14">
         <v>68</v>
       </c>
-      <c r="J17" s="14">
-        <v>61</v>
-      </c>
       <c r="K17" s="15">
-        <v>11.475409836065</v>
+        <v>8.823529411764</v>
       </c>
       <c r="L17" s="15">
-        <v>38.775510204081</v>
+        <v>32.142857142857</v>
       </c>
       <c r="M17" s="15">
-        <v>112.5</v>
+        <v>117.647058823529</v>
       </c>
       <c r="N17" s="15">
-        <v>1.492537313432</v>
+        <v>7.246376811594</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-33.333333333333</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H18" s="15">
-        <v>-61.111111111111</v>
+        <v>-70.588235294117</v>
       </c>
       <c r="I18" s="14">
         <v>23</v>
@@ -1043,13 +1043,13 @@
         <v>-51.063829787234</v>
       </c>
       <c r="L18" s="15">
-        <v>-32.352941176470</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="M18" s="15">
-        <v>-43.902439024390</v>
+        <v>-46.511627906976</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.698412698412</v>
+        <v>-93.154761904761</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E19" s="15">
-        <v>-52.941176470588</v>
+        <v>-69.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="H19" s="15">
-        <v>-36.734693877551</v>
+        <v>-52.054794520547</v>
       </c>
       <c r="I19" s="14">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="J19" s="14">
-        <v>145</v>
+        <v>181</v>
       </c>
       <c r="K19" s="15">
-        <v>-14.482758620689</v>
+        <v>-25.414364640884</v>
       </c>
       <c r="L19" s="15">
-        <v>-42.056074766355</v>
+        <v>-41.558441558441</v>
       </c>
       <c r="M19" s="15">
-        <v>53.086419753086</v>
+        <v>48.351648351648</v>
       </c>
       <c r="N19" s="15">
-        <v>10.714285714285</v>
+        <v>9.756097560975</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>8</v>
       </c>
       <c r="D20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H20" s="15">
-        <v>-66.666666666666</v>
+        <v>-30</v>
       </c>
       <c r="I20" s="14">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="J20" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>2.777777777777</v>
       </c>
       <c r="L20" s="15">
-        <v>-37.735849056603</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="M20" s="15">
-        <v>112.903225806452</v>
+        <v>111.428571428571</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.987261146496</v>
+        <v>-85.258964143426</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D21" s="17">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E21" s="18">
-        <v>-30.303030303030</v>
+        <v>-50</v>
       </c>
       <c r="F21" s="17">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="G21" s="17">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="H21" s="18">
-        <v>-25.423728813559</v>
+        <v>-28.676470588235</v>
       </c>
       <c r="I21" s="17">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="J21" s="17">
-        <v>355</v>
+        <v>407</v>
       </c>
       <c r="K21" s="18">
-        <v>-5.915492957746</v>
+        <v>-11.547911547911</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.942350332594</v>
+        <v>-25.773195876288</v>
       </c>
       <c r="M21" s="18">
-        <v>45.851528384279</v>
+        <v>44</v>
       </c>
       <c r="N21" s="18">
-        <v>-71.256454388984</v>
+        <v>-70.850202429149</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1191,11 +1191,11 @@
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>-100</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1206,11 +1206,11 @@
       <c r="K22" s="15">
         <v>33.333333333333</v>
       </c>
-      <c r="L22" s="13" t="s">
-        <v>21</v>
+      <c r="L22" s="15">
+        <v>300</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="14">
+      <c r="C23" s="14">
         <v>2</v>
       </c>
-      <c r="E23" s="15">
-        <v>-100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J23" s="14">
         <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-31.25</v>
+        <v>-18.75</v>
       </c>
       <c r="L23" s="15">
-        <v>-47.619047619047</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="M23" s="15">
-        <v>-26.666666666666</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="F24" s="14">
         <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="H24" s="15">
-        <v>4.347826086956</v>
+        <v>-25.773195876288</v>
       </c>
       <c r="I24" s="14">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="J24" s="14">
-        <v>245</v>
+        <v>291</v>
       </c>
       <c r="K24" s="15">
-        <v>16.734693877551</v>
+        <v>7.216494845360</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.917197452229</v>
+        <v>-6.586826347305</v>
       </c>
       <c r="M24" s="15">
-        <v>30</v>
+        <v>30.543933054393</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="F25" s="14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>8.333333333333</v>
+        <v>-48.780487804878</v>
       </c>
       <c r="I25" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J25" s="14">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="K25" s="15">
-        <v>1.587301587301</v>
+        <v>-16.867469879518</v>
       </c>
       <c r="L25" s="15">
-        <v>-50.387596899224</v>
+        <v>-50.359712230215</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-28.571428571428</v>
+        <v>50</v>
       </c>
       <c r="F26" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
         <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>-2.857142857142</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="J26" s="14">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="K26" s="15">
-        <v>17.525773195876</v>
+        <v>19.047619047619</v>
       </c>
       <c r="L26" s="15">
-        <v>26.666666666666</v>
+        <v>28.865979381443</v>
       </c>
       <c r="M26" s="15">
-        <v>26.666666666666</v>
+        <v>30.208333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>2</v>
-      </c>
-      <c r="D27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>7</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>8</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>166.666666666667</v>
+        <v>600</v>
       </c>
       <c r="I27" s="14">
         <v>15</v>
@@ -1412,7 +1412,7 @@
         <v>66.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>100</v>
+        <v>4</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>166.666666666667</v>
+        <v>233.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J28" s="14">
         <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>110.526315789474</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,10 +1488,10 @@
         <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="L29" s="15">
         <v>600</v>
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,10 +1529,10 @@
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="L30" s="15">
         <v>200</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>Rape</t>
+  </si>
+  <si>
     <t>***.*</t>
-  </si>
-  <si>
-    <t>Rape</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -854,29 +854,29 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="14">
         <v>4</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>300</v>
       </c>
       <c r="L14" s="15">
         <v>300</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="13" t="s">
         <v>20</v>
@@ -899,16 +899,16 @@
         <v>20</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="14">
         <v>14</v>
@@ -936,38 +936,38 @@
       <c r="C16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-33.333333333333</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>22</v>
       </c>
       <c r="F16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>83.333333333333</v>
+        <v>160</v>
       </c>
       <c r="I16" s="14">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J16" s="14">
         <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>12.5</v>
+        <v>21.875</v>
       </c>
       <c r="L16" s="15">
         <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-12.195121951219</v>
+        <v>-9.302325581395</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.538461538461</v>
+        <v>-81.339712918660</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F17" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>30</v>
+        <v>61.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J17" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K17" s="15">
-        <v>8.823529411764</v>
+        <v>16.901408450704</v>
       </c>
       <c r="L17" s="15">
-        <v>32.142857142857</v>
+        <v>43.103448275862</v>
       </c>
       <c r="M17" s="15">
-        <v>117.647058823529</v>
+        <v>130.555555555556</v>
       </c>
       <c r="N17" s="15">
-        <v>7.246376811594</v>
+        <v>15.277777777777</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>2</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H18" s="15">
-        <v>-70.588235294117</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K18" s="15">
-        <v>-51.063829787234</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.111111111111</v>
+        <v>-34.210526315789</v>
       </c>
       <c r="M18" s="15">
-        <v>-46.511627906976</v>
+        <v>-41.860465116279</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.154761904761</v>
+        <v>-93.093922651933</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-69.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
         <v>35</v>
       </c>
       <c r="G19" s="14">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="H19" s="15">
-        <v>-52.054794520547</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="I19" s="14">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J19" s="14">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="K19" s="15">
-        <v>-25.414364640884</v>
+        <v>-27.692307692307</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.558441558441</v>
+        <v>-42.213114754098</v>
       </c>
       <c r="M19" s="15">
-        <v>48.351648351648</v>
+        <v>45.360824742268</v>
       </c>
       <c r="N19" s="15">
-        <v>9.756097560975</v>
+        <v>11.023622047244</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>6</v>
+      </c>
+      <c r="D20" s="14">
         <v>8</v>
       </c>
-      <c r="D20" s="14">
-        <v>6</v>
-      </c>
       <c r="E20" s="15">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F20" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H20" s="15">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J20" s="14">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="K20" s="15">
-        <v>2.777777777777</v>
+        <v>-1.25</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.928571428571</v>
+        <v>-32.478632478632</v>
       </c>
       <c r="M20" s="15">
-        <v>111.428571428571</v>
+        <v>102.564102564103</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.258964143426</v>
+        <v>-85.557586837294</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D21" s="17">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="E21" s="18">
-        <v>-50</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="F21" s="17">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="G21" s="17">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.676470588235</v>
+        <v>-26.618705035971</v>
       </c>
       <c r="I21" s="17">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="J21" s="17">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.547911547911</v>
+        <v>-11.697247706422</v>
       </c>
       <c r="L21" s="18">
-        <v>-25.773195876288</v>
+        <v>-24.657534246575</v>
       </c>
       <c r="M21" s="18">
-        <v>44</v>
+        <v>45.833333333333</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.850202429149</v>
+        <v>-70.987189148455</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1207,13 +1207,13 @@
         <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,13 +1221,13 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F23" s="14">
         <v>3</v>
@@ -1239,22 +1239,22 @@
         <v>50</v>
       </c>
       <c r="I23" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="14">
         <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-18.75</v>
+        <v>-12.5</v>
       </c>
       <c r="L23" s="15">
-        <v>-43.478260869565</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M23" s="15">
-        <v>-13.333333333333</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-43.478260869565</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G24" s="14">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="H24" s="15">
-        <v>-25.773195876288</v>
+        <v>-37.962962962963</v>
       </c>
       <c r="I24" s="14">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="J24" s="14">
-        <v>291</v>
+        <v>315</v>
       </c>
       <c r="K24" s="15">
-        <v>7.216494845360</v>
+        <v>5.079365079365</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.586826347305</v>
+        <v>-5.698005698005</v>
       </c>
       <c r="M24" s="15">
-        <v>30.543933054393</v>
+        <v>26.819923371647</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1303,40 +1303,40 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E25" s="15">
-        <v>-70</v>
+        <v>-10</v>
       </c>
       <c r="F25" s="14">
         <v>21</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H25" s="15">
-        <v>-48.780487804878</v>
+        <v>-54.347826086956</v>
       </c>
       <c r="I25" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J25" s="14">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.867469879518</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="L25" s="15">
-        <v>-50.359712230215</v>
+        <v>-47.297297297297</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,122 +1344,122 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="J26" s="14">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K26" s="15">
-        <v>19.047619047619</v>
+        <v>21.100917431192</v>
       </c>
       <c r="L26" s="15">
-        <v>28.865979381443</v>
+        <v>32</v>
       </c>
       <c r="M26" s="15">
-        <v>30.208333333333</v>
+        <v>23.364485981308</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I27" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>66.666666666666</v>
+        <v>88.888888888888</v>
       </c>
       <c r="L27" s="15">
-        <v>150</v>
+        <v>183.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>4</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>233.333333333333</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
         <v>40</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>300</v>
+        <v>263.636363636364</v>
       </c>
       <c r="L28" s="15">
-        <v>110.526315789474</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -1470,7 +1470,7 @@
         <v>20</v>
       </c>
       <c r="D29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="15">
         <v>-100</v>
@@ -1479,7 +1479,7 @@
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,16 +1488,16 @@
         <v>7</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="L29" s="15">
         <v>600</v>
       </c>
       <c r="M29" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="N29" s="15">
         <v>133.333333333333</v>
@@ -1520,7 +1520,7 @@
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,16 +1529,16 @@
         <v>3</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>200</v>
       </c>
       <c r="M30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="N30" s="15">
         <v>0</v>
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
@@ -1564,25 +1564,25 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I33" s="14">
         <v>3</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="14">
         <v>36</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -202,10 +202,10 @@
     <t>0</t>
   </si>
   <si>
+    <t>***.*</t>
+  </si>
+  <si>
     <t>Rape</t>
-  </si>
-  <si>
-    <t>***.*</t>
   </si>
   <si>
     <t>Robbery</t>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -890,43 +890,43 @@
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>200</v>
+      </c>
       <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>22</v>
+        <v>5</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>400</v>
       </c>
       <c r="I15" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>100</v>
+        <v>112.5</v>
       </c>
       <c r="L15" s="15">
-        <v>1300</v>
+        <v>1600</v>
       </c>
       <c r="M15" s="15">
-        <v>366.666666666667</v>
+        <v>466.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>75</v>
+        <v>112.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>160</v>
+        <v>225</v>
       </c>
       <c r="I16" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
         <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>21.875</v>
+        <v>31.25</v>
       </c>
       <c r="L16" s="15">
         <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-9.302325581395</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="N16" s="15">
-        <v>-81.339712918660</v>
+        <v>-80.909090909090</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>166.666666666667</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>61.111111111111</v>
+        <v>25</v>
       </c>
       <c r="I17" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J17" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K17" s="15">
-        <v>16.901408450704</v>
+        <v>15.789473684210</v>
       </c>
       <c r="L17" s="15">
-        <v>43.103448275862</v>
+        <v>39.682539682539</v>
       </c>
       <c r="M17" s="15">
-        <v>130.555555555556</v>
+        <v>131.578947368421</v>
       </c>
       <c r="N17" s="15">
-        <v>15.277777777777</v>
+        <v>6.024096385542</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-71.428571428571</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-52.727272727272</v>
       </c>
       <c r="L18" s="15">
-        <v>-34.210526315789</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="M18" s="15">
-        <v>-41.860465116279</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.093922651933</v>
+        <v>-93.246753246753</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G19" s="14">
         <v>77</v>
       </c>
       <c r="H19" s="15">
-        <v>-54.545454545454</v>
+        <v>-51.948051948051</v>
       </c>
       <c r="I19" s="14">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="J19" s="14">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="K19" s="15">
-        <v>-27.692307692307</v>
+        <v>-25.365853658536</v>
       </c>
       <c r="L19" s="15">
-        <v>-42.213114754098</v>
+        <v>-41.153846153846</v>
       </c>
       <c r="M19" s="15">
-        <v>45.360824742268</v>
+        <v>50</v>
       </c>
       <c r="N19" s="15">
-        <v>11.023622047244</v>
+        <v>11.678832116788</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G20" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-34.615384615384</v>
       </c>
       <c r="I20" s="14">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="J20" s="14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K20" s="15">
-        <v>-1.25</v>
+        <v>-2.352941176470</v>
       </c>
       <c r="L20" s="15">
-        <v>-32.478632478632</v>
+        <v>-30.833333333333</v>
       </c>
       <c r="M20" s="15">
-        <v>102.564102564103</v>
+        <v>93.023255813953</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.557586837294</v>
+        <v>-85.836177474402</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D21" s="17">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.793103448275</v>
+        <v>3.846153846153</v>
       </c>
       <c r="F21" s="17">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G21" s="17">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.618705035971</v>
+        <v>-26.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>385</v>
+        <v>413</v>
       </c>
       <c r="J21" s="17">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.697247706422</v>
+        <v>-10.606060606060</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.657534246575</v>
+        <v>-23.800738007380</v>
       </c>
       <c r="M21" s="18">
-        <v>45.833333333333</v>
+        <v>47.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.987189148455</v>
+        <v>-70.935960591133</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1186,7 +1186,7 @@
         <v>20</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1195,7 +1195,7 @@
         <v>20</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
@@ -1210,10 +1210,10 @@
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-42.857142857142</v>
+        <v>-50</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1221,40 +1221,40 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
         <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I23" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J23" s="14">
         <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-41.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>-6.666666666666</v>
+        <v>6.666666666666</v>
       </c>
       <c r="N23" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1262,40 +1262,40 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D24" s="14">
         <v>24</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G24" s="14">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H24" s="15">
-        <v>-37.962962962963</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I24" s="14">
-        <v>331</v>
+        <v>355</v>
       </c>
       <c r="J24" s="14">
-        <v>315</v>
+        <v>339</v>
       </c>
       <c r="K24" s="15">
-        <v>5.079365079365</v>
+        <v>4.719764011799</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.698005698005</v>
+        <v>-5.835543766578</v>
       </c>
       <c r="M24" s="15">
-        <v>26.819923371647</v>
+        <v>25.441696113074</v>
       </c>
       <c r="N24" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1306,37 +1306,37 @@
         <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>-10</v>
+        <v>80</v>
       </c>
       <c r="F25" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G25" s="14">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H25" s="15">
-        <v>-54.347826086956</v>
+        <v>-36.585365853658</v>
       </c>
       <c r="I25" s="14">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="J25" s="14">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K25" s="15">
-        <v>-16.129032258064</v>
+        <v>-11.224489795918</v>
       </c>
       <c r="L25" s="15">
-        <v>-47.297297297297</v>
+        <v>-44.936708860759</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N25" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1344,40 +1344,40 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>-13.636363636363</v>
       </c>
       <c r="I26" s="14">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="J26" s="14">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="K26" s="15">
-        <v>21.100917431192</v>
+        <v>11.811023622047</v>
       </c>
       <c r="L26" s="15">
-        <v>32</v>
+        <v>27.927927927927</v>
       </c>
       <c r="M26" s="15">
-        <v>23.364485981308</v>
+        <v>26.785714285714</v>
       </c>
       <c r="N26" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -1385,163 +1385,163 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>5</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>400</v>
+      </c>
+      <c r="F27" s="14">
+        <v>9</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
+      <c r="H27" s="15">
+        <v>350</v>
+      </c>
+      <c r="I27" s="14">
         <v>22</v>
       </c>
-      <c r="F27" s="14">
-        <v>5</v>
-      </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>400</v>
-      </c>
-      <c r="I27" s="14">
-        <v>17</v>
-      </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>88.888888888888</v>
+        <v>120</v>
       </c>
       <c r="L27" s="15">
-        <v>183.333333333333</v>
+        <v>266.666666666667</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N27" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" s="14">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="I28" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>263.636363636364</v>
+        <v>290.909090909091</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="M28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N28" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>2</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>4</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="I29" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J29" s="14">
         <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M29" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="N29" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
         <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G30" s="14">
         <v>3</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="14">
         <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L30" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M30" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N30" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1555,7 +1555,7 @@
         <v>20</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>2</v>
@@ -1564,7 +1564,7 @@
         <v>20</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>5</v>
@@ -1573,16 +1573,16 @@
         <v>20</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L31" s="15">
         <v>400</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N31" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:14">
@@ -1614,7 +1614,7 @@
         <v>20</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>
@@ -1623,7 +1623,7 @@
         <v>20</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I33" s="14">
         <v>3</v>
@@ -1632,16 +1632,16 @@
         <v>20</v>
       </c>
       <c r="K33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="N33" s="13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -1772,7 +1772,7 @@
     </row>
     <row r="40" spans="1:14">
       <c r="A40" s="13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C40" s="14">
         <v>36</v>

--- a/data/source/weekly/cs-en-us-050pct.xlsx
+++ b/data/source/weekly/cs-en-us-050pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>3</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>200</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="I15" s="14">
         <v>17</v>
@@ -920,7 +920,7 @@
         <v>112.5</v>
       </c>
       <c r="L15" s="15">
-        <v>1600</v>
+        <v>466.666666666667</v>
       </c>
       <c r="M15" s="15">
         <v>466.666666666667</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>225</v>
+        <v>60</v>
       </c>
       <c r="I16" s="14">
         <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>31.25</v>
+        <v>23.529411764705</v>
       </c>
       <c r="L16" s="15">
         <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-10.638297872340</v>
+        <v>-19.230769230769</v>
       </c>
       <c r="N16" s="15">
-        <v>-80.909090909090</v>
+        <v>-81.415929203539</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
         <v>5</v>
       </c>
       <c r="E17" s="15">
+        <v>-80</v>
+      </c>
+      <c r="F17" s="14">
+        <v>20</v>
+      </c>
+      <c r="G17" s="14">
+        <v>20</v>
+      </c>
+      <c r="H17" s="15">
         <v>0</v>
       </c>
-      <c r="F17" s="14">
-        <v>25</v>
-      </c>
-      <c r="G17" s="14">
-        <v>20</v>
-      </c>
-      <c r="H17" s="15">
-        <v>25</v>
-      </c>
       <c r="I17" s="14">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="K17" s="15">
-        <v>15.789473684210</v>
+        <v>9.876543209876</v>
       </c>
       <c r="L17" s="15">
-        <v>39.682539682539</v>
+        <v>30.882352941176</v>
       </c>
       <c r="M17" s="15">
-        <v>131.578947368421</v>
+        <v>122.5</v>
       </c>
       <c r="N17" s="15">
-        <v>6.024096385542</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>2</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-60</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-45.454545454545</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I18" s="14">
         <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K18" s="15">
-        <v>-52.727272727272</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>-36.585365853658</v>
+        <v>-42.222222222222</v>
       </c>
       <c r="M18" s="15">
-        <v>-40.909090909090</v>
+        <v>-42.222222222222</v>
       </c>
       <c r="N18" s="15">
-        <v>-93.246753246753</v>
+        <v>-93.532338308457</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>27.272727272727</v>
       </c>
       <c r="F19" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="G19" s="14">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H19" s="15">
-        <v>-51.948051948051</v>
+        <v>-39.436619718309</v>
       </c>
       <c r="I19" s="14">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="J19" s="14">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="K19" s="15">
-        <v>-25.365853658536</v>
+        <v>-21.759259259259</v>
       </c>
       <c r="L19" s="15">
-        <v>-41.153846153846</v>
+        <v>-36.940298507462</v>
       </c>
       <c r="M19" s="15">
-        <v>50</v>
+        <v>56.481481481481</v>
       </c>
       <c r="N19" s="15">
-        <v>11.678832116788</v>
+        <v>13.422818791946</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G20" s="14">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="H20" s="15">
-        <v>-34.615384615384</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J20" s="14">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K20" s="15">
-        <v>-2.352941176470</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-30.833333333333</v>
+        <v>-30.081300813008</v>
       </c>
       <c r="M20" s="15">
-        <v>93.023255813953</v>
+        <v>91.111111111111</v>
       </c>
       <c r="N20" s="15">
-        <v>-85.836177474402</v>
+        <v>-86.370839936608</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>3.846153846153</v>
+        <v>-10</v>
       </c>
       <c r="F21" s="17">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G21" s="17">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.428571428571</v>
+        <v>-22.047244094488</v>
       </c>
       <c r="I21" s="17">
-        <v>413</v>
+        <v>433</v>
       </c>
       <c r="J21" s="17">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="K21" s="18">
-        <v>-10.606060606060</v>
+        <v>-10.165975103734</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.800738007380</v>
+        <v>-23.226950354609</v>
       </c>
       <c r="M21" s="18">
-        <v>47.5</v>
+        <v>46.283783783783</v>
       </c>
       <c r="N21" s="18">
-        <v>-70.935960591133</v>
+        <v>-71.267418712674</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>4</v>
       </c>
       <c r="J22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>100</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1232,26 +1232,26 @@
       <c r="F23" s="14">
         <v>5</v>
       </c>
-      <c r="G23" s="14">
-        <v>2</v>
-      </c>
-      <c r="H23" s="15">
-        <v>150</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J23" s="14">
         <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-6.25</v>
       </c>
       <c r="L23" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="M23" s="15">
-        <v>6.666666666666</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>177.777777777778</v>
       </c>
       <c r="F24" s="14">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G24" s="14">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15">
-        <v>-27.272727272727</v>
+        <v>-9.708737864077</v>
       </c>
       <c r="I24" s="14">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="J24" s="14">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="K24" s="15">
-        <v>4.719764011799</v>
+        <v>8.908045977011</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.835543766578</v>
+        <v>-2.319587628865</v>
       </c>
       <c r="M24" s="15">
-        <v>25.441696113074</v>
+        <v>26.755852842809</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
         <v>5</v>
       </c>
       <c r="E25" s="15">
-        <v>80</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G25" s="14">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H25" s="15">
-        <v>-36.585365853658</v>
+        <v>-30</v>
       </c>
       <c r="I25" s="14">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="J25" s="14">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.224489795918</v>
+        <v>-11.650485436893</v>
       </c>
       <c r="L25" s="15">
-        <v>-44.936708860759</v>
+        <v>-43.827160493827</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G26" s="14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-13.636363636363</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="J26" s="14">
-        <v>127</v>
+        <v>139</v>
       </c>
       <c r="K26" s="15">
-        <v>11.811023622047</v>
+        <v>9.352517985611</v>
       </c>
       <c r="L26" s="15">
-        <v>27.927927927927</v>
+        <v>29.914529914529</v>
       </c>
       <c r="M26" s="15">
-        <v>26.785714285714</v>
+        <v>23.577235772357</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>5</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>400</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
         <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="I27" s="14">
         <v>22</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L27" s="15">
-        <v>266.666666666667</v>
+        <v>175</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,7 +1426,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,22 +1438,22 @@
         <v>9</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>350</v>
+        <v>800</v>
       </c>
       <c r="I28" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>290.909090909091</v>
+        <v>318.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>115</v>
+        <v>109.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I29" s="14">
         <v>8</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1520,10 +1520,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I30" s="14">
         <v>4</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>
@@ -1576,7 +1576,7 @@
         <v>21</v>
       </c>
       <c r="L31" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
